--- a/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Reels Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Reels Variants" sheetId="2" r:id="rId2"/>
+    <sheet name="reel" sheetId="1" r:id="rId1"/>
+    <sheet name="baitcasting_reel_detail" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -451,8 +451,8 @@
       <c r="A2" t="str">
         <v>DRE5000</v>
       </c>
-      <c r="B2" t="str">
-        <v>B-DAIWA</v>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
         <v>IM Z リミットブレイカー TW HD-C</v>
@@ -476,10 +476,10 @@
         <v>images/daiwa_reels/IM_Z_リミットブレイカー_TW_HD-C_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -502,8 +502,8 @@
       <c r="A3" t="str">
         <v>DRE5001</v>
       </c>
-      <c r="B3" t="str">
-        <v>B-DAIWA</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v>IM Z TW 200-C</v>
@@ -527,10 +527,10 @@
         <v>images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -553,8 +553,8 @@
       <c r="A4" t="str">
         <v>DRE5002</v>
       </c>
-      <c r="B4" t="str">
-        <v>B-DAIWA</v>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v>IM Z TW100-C</v>
@@ -578,10 +578,10 @@
         <v>images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -605,8 +605,8 @@
       <c r="A5" t="str">
         <v>DRE5003</v>
       </c>
-      <c r="B5" t="str">
-        <v>B-DAIWA</v>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" t="str">
         <v>スティーズ リミテッド CT SV TW</v>
@@ -630,10 +630,10 @@
         <v>images/daiwa_reels/スティーズ_リミテッド_CT_SV_TW_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -656,8 +656,8 @@
       <c r="A6" t="str">
         <v>DRE5004</v>
       </c>
-      <c r="B6" t="str">
-        <v>B-DAIWA</v>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>スティーズ SV ライト TW</v>
@@ -681,10 +681,10 @@
         <v>images/daiwa_reels/スティーズ_SV_ライト_TW_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -705,8 +705,8 @@
       <c r="A7" t="str">
         <v>DRE5005</v>
       </c>
-      <c r="B7" t="str">
-        <v>B-DAIWA</v>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>スティーズ SV TW100</v>
@@ -730,10 +730,10 @@
         <v>images/daiwa_reels/スティーズ_SV_TW100_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -756,8 +756,8 @@
       <c r="A8" t="str">
         <v>DRE5006</v>
       </c>
-      <c r="B8" t="str">
-        <v>B-DAIWA</v>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>スティーズ AIR TW</v>
@@ -781,10 +781,10 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -807,8 +807,8 @@
       <c r="A9" t="str">
         <v>DRE5007</v>
       </c>
-      <c r="B9" t="str">
-        <v>B-DAIWA</v>
+      <c r="B9">
+        <v>2</v>
       </c>
       <c r="C9" t="str">
         <v>リョウガ</v>
@@ -832,10 +832,10 @@
         <v>images/daiwa_reels/リョウガ_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -860,8 +860,8 @@
       <c r="A10" t="str">
         <v>DRE5008</v>
       </c>
-      <c r="B10" t="str">
-        <v>B-DAIWA</v>
+      <c r="B10">
+        <v>2</v>
       </c>
       <c r="C10" t="str">
         <v>スティーズ CT SV TW</v>
@@ -885,10 +885,10 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -909,8 +909,8 @@
       <c r="A11" t="str">
         <v>DRE5009</v>
       </c>
-      <c r="B11" t="str">
-        <v>B-DAIWA</v>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="str">
         <v>ジリオン TW HD</v>
@@ -934,10 +934,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_tw_hd_22/__icsFiles/afieldfile/2022/04/08/main.jpg?rev=dd8848fe936e4b268b8bdb9e4b33a4df</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -961,8 +961,8 @@
       <c r="A12" t="str">
         <v>DRE5010</v>
       </c>
-      <c r="B12" t="str">
-        <v>B-DAIWA</v>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" t="str">
         <v>月下美人 BF TW PE SP</v>
@@ -986,10 +986,10 @@
         <v>images/daiwa_reels/月下美人_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1013,8 +1013,8 @@
       <c r="A13" t="str">
         <v>DRE5011</v>
       </c>
-      <c r="B13" t="str">
-        <v>B-DAIWA</v>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>モアザン PE TW</v>
@@ -1038,10 +1038,10 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1063,8 +1063,8 @@
       <c r="A14" t="str">
         <v>DRE5012</v>
       </c>
-      <c r="B14" t="str">
-        <v>B-DAIWA</v>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
         <v>シルバーウルフ CT SV TW　PE SPECIAL</v>
@@ -1088,10 +1088,10 @@
         <v>images/daiwa_reels/シルバーウルフ_CT_SV_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1116,8 +1116,8 @@
       <c r="A15" t="str">
         <v>DRE5013</v>
       </c>
-      <c r="B15" t="str">
-        <v>B-DAIWA</v>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="C15" t="str">
         <v>スティーズ A II TW</v>
@@ -1141,10 +1141,10 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1165,8 +1165,8 @@
       <c r="A16" t="str">
         <v>DRE5014</v>
       </c>
-      <c r="B16" t="str">
-        <v>B-DAIWA</v>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>スティーズ A TW HLC</v>
@@ -1190,10 +1190,10 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1216,8 +1216,8 @@
       <c r="A17" t="str">
         <v>DRE5015</v>
       </c>
-      <c r="B17" t="str">
-        <v>B-DAIWA</v>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>HRF TW PE SP</v>
@@ -1241,10 +1241,10 @@
         <v>images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1269,8 +1269,8 @@
       <c r="A18" t="str">
         <v>DRE5016</v>
       </c>
-      <c r="B18" t="str">
-        <v>B-DAIWA</v>
+      <c r="B18">
+        <v>2</v>
       </c>
       <c r="C18" t="str">
         <v>シルバーウルフ SV TW PE SPECIAL</v>
@@ -1294,10 +1294,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/salt_rl/silverwolf_sv_tw/__icsFiles/artimage/2022/04/01/c_041110017/main_tx_im01_1.jpg?rev=6d195f85744643bda6ef194759f4c436</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1318,8 +1318,8 @@
       <c r="A19" t="str">
         <v>DRE5017</v>
       </c>
-      <c r="B19" t="str">
-        <v>B-DAIWA</v>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>シルバークリーク エア TW ストリームカスタム</v>
@@ -1343,10 +1343,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/silvercreek_air_tw_sc/__icsFiles/artimage/2022/03/29/c_041101086/main_tx_im01_3.jpg?rev=d0db4f46700344e7893e0f732daf59a2</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1369,8 +1369,8 @@
       <c r="A20" t="str">
         <v>DRE5018</v>
       </c>
-      <c r="B20" t="str">
-        <v>B-DAIWA</v>
+      <c r="B20">
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>SS AIR TW</v>
@@ -1394,10 +1394,10 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1421,8 +1421,8 @@
       <c r="A21" t="str">
         <v>DRE5019</v>
       </c>
-      <c r="B21" t="str">
-        <v>B-DAIWA</v>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="str">
         <v>アルファスBF TW</v>
@@ -1446,10 +1446,10 @@
         <v>images/daiwa_reels/アルファスBF_TW_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1474,8 +1474,8 @@
       <c r="A22" t="str">
         <v>DRE5020</v>
       </c>
-      <c r="B22" t="str">
-        <v>B-DAIWA</v>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>ZILLION SV TW</v>
@@ -1499,10 +1499,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_sv_tw21/__icsFiles/artimage/2022/05/02/c_041101076/main_bg02_1.jpg?rev=eb0a7bf7b3584f528da16f4584f37003</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1525,8 +1525,8 @@
       <c r="A23" t="str">
         <v>DRE5021</v>
       </c>
-      <c r="B23" t="str">
-        <v>B-DAIWA</v>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="str">
         <v>ソルティスト TW PE SPECIAL</v>
@@ -1550,10 +1550,10 @@
         <v>images/daiwa_reels/ソルティスト_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1577,8 +1577,8 @@
       <c r="A24" t="str">
         <v>DRE5022</v>
       </c>
-      <c r="B24" t="str">
-        <v>B-DAIWA</v>
+      <c r="B24">
+        <v>2</v>
       </c>
       <c r="C24" t="str">
         <v>TATULA TW 300/400</v>
@@ -1602,10 +1602,10 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1628,8 +1628,8 @@
       <c r="A25" t="str">
         <v>DRE5023</v>
       </c>
-      <c r="B25" t="str">
-        <v>B-DAIWA</v>
+      <c r="B25">
+        <v>2</v>
       </c>
       <c r="C25" t="str">
         <v>アルファス SV TW</v>
@@ -1653,10 +1653,10 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1677,8 +1677,8 @@
       <c r="A26" t="str">
         <v>DRE5024</v>
       </c>
-      <c r="B26" t="str">
-        <v>B-DAIWA</v>
+      <c r="B26">
+        <v>2</v>
       </c>
       <c r="C26" t="str">
         <v>タトゥーラ BF TW</v>
@@ -1702,10 +1702,10 @@
         <v>images/daiwa_reels/タトゥーラ_BF_TW_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1730,8 +1730,8 @@
       <c r="A27" t="str">
         <v>DRE5025</v>
       </c>
-      <c r="B27" t="str">
-        <v>B-DAIWA</v>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>タトゥーラ TW 200</v>
@@ -1755,10 +1755,10 @@
         <v>images/daiwa_reels/タトゥーラ_TW_200_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1784,8 +1784,8 @@
       <c r="A28" t="str">
         <v>DRE5026</v>
       </c>
-      <c r="B28" t="str">
-        <v>B-DAIWA</v>
+      <c r="B28">
+        <v>2</v>
       </c>
       <c r="C28" t="str">
         <v>タトゥーラ SV TW</v>
@@ -1809,10 +1809,10 @@
         <v>images/daiwa_reels/タトゥーラ_SV_TW_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1836,8 +1836,8 @@
       <c r="A29" t="str">
         <v>DRE5027</v>
       </c>
-      <c r="B29" t="str">
-        <v>B-DAIWA</v>
+      <c r="B29">
+        <v>2</v>
       </c>
       <c r="C29" t="str">
         <v>タトゥーラ TW 100</v>
@@ -1861,10 +1861,10 @@
         <v>images/daiwa_reels/タトゥーラ_TW_100_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1888,8 +1888,8 @@
       <c r="A30" t="str">
         <v>DRE5028</v>
       </c>
-      <c r="B30" t="str">
-        <v>B-DAIWA</v>
+      <c r="B30">
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>バス  X  100</v>
@@ -1913,10 +1913,10 @@
         <v>images/daiwa_reels/バス__X__100_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1937,8 +1937,8 @@
       <c r="A31" t="str">
         <v>DRE5029</v>
       </c>
-      <c r="B31" t="str">
-        <v>B-DAIWA</v>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="str">
         <v>PR100</v>
@@ -1962,10 +1962,10 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -2109,7 +2109,7 @@
         <v>handle_style</v>
       </c>
       <c r="AM1" t="str">
-        <v>MAX DURABILITY</v>
+        <v>MAX_DURABILITY</v>
       </c>
     </row>
     <row r="2">
@@ -2159,10 +2159,10 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R2" t="str">
         <v>38</v>
@@ -2278,10 +2278,10 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R3" t="str">
         <v>38</v>
@@ -2397,10 +2397,10 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R4" t="str">
         <v>38</v>
@@ -2516,10 +2516,10 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R5" t="str">
         <v>38</v>
@@ -2635,10 +2635,10 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R6" t="str">
         <v>38</v>
@@ -2754,10 +2754,10 @@
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R7" t="str">
         <v>38</v>
@@ -2873,10 +2873,10 @@
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R8" t="str">
         <v>34</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R9" t="str">
         <v>34</v>
@@ -3111,10 +3111,10 @@
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R10" t="str">
         <v>34</v>
@@ -3230,10 +3230,10 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R11" t="str">
         <v>34</v>
@@ -3349,10 +3349,10 @@
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R12" t="str">
         <v>34</v>
@@ -3468,10 +3468,10 @@
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R13" t="str">
         <v>34</v>
@@ -3587,10 +3587,10 @@
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R14" t="str">
         <v>φ30</v>
@@ -3706,10 +3706,10 @@
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R15" t="str">
         <v>φ30</v>
@@ -3825,10 +3825,10 @@
         <v/>
       </c>
       <c r="P16" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R16" t="str">
         <v>32</v>
@@ -3944,10 +3944,10 @@
         <v/>
       </c>
       <c r="P17" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R17" t="str">
         <v>32</v>
@@ -4063,10 +4063,10 @@
         <v/>
       </c>
       <c r="P18" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R18" t="str">
         <v>32</v>
@@ -4182,10 +4182,10 @@
         <v/>
       </c>
       <c r="P19" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R19" t="str">
         <v>32</v>
@@ -4301,10 +4301,10 @@
         <v/>
       </c>
       <c r="P20" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R20" t="str">
         <v>32</v>
@@ -4420,10 +4420,10 @@
         <v/>
       </c>
       <c r="P21" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R21" t="str">
         <v>32</v>
@@ -4539,10 +4539,10 @@
         <v/>
       </c>
       <c r="P22" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R22" t="str">
         <v>32</v>
@@ -4658,10 +4658,10 @@
         <v/>
       </c>
       <c r="P23" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R23" t="str">
         <v>32</v>
@@ -4777,10 +4777,10 @@
         <v/>
       </c>
       <c r="P24" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R24" t="str">
         <v>32</v>
@@ -4896,10 +4896,10 @@
         <v/>
       </c>
       <c r="P25" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R25" t="str">
         <v>32</v>
@@ -5015,10 +5015,10 @@
         <v/>
       </c>
       <c r="P26" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R26" t="str">
         <v>28</v>
@@ -5134,10 +5134,10 @@
         <v/>
       </c>
       <c r="P27" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R27" t="str">
         <v>28</v>
@@ -5253,10 +5253,10 @@
         <v/>
       </c>
       <c r="P28" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R28" t="str">
         <v>28</v>
@@ -5372,10 +5372,10 @@
         <v/>
       </c>
       <c r="P29" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R29" t="str">
         <v>28</v>
@@ -5491,10 +5491,10 @@
         <v/>
       </c>
       <c r="P30" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R30" t="str">
         <v>34</v>
@@ -5610,10 +5610,10 @@
         <v/>
       </c>
       <c r="P31" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R31" t="str">
         <v>34</v>
@@ -5729,10 +5729,10 @@
         <v/>
       </c>
       <c r="P32" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R32" t="str">
         <v>34</v>
@@ -5848,10 +5848,10 @@
         <v/>
       </c>
       <c r="P33" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R33" t="str">
         <v>34</v>
@@ -5967,10 +5967,10 @@
         <v/>
       </c>
       <c r="P34" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R34" t="str">
         <v>36</v>
@@ -6086,10 +6086,10 @@
         <v/>
       </c>
       <c r="P35" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R35" t="str">
         <v>36</v>
@@ -6205,10 +6205,10 @@
         <v/>
       </c>
       <c r="P36" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R36" t="str">
         <v>36</v>
@@ -6324,10 +6324,10 @@
         <v/>
       </c>
       <c r="P37" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R37" t="str">
         <v>36</v>
@@ -6443,10 +6443,10 @@
         <v/>
       </c>
       <c r="P38" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R38" t="str">
         <v>30</v>
@@ -6562,10 +6562,10 @@
         <v/>
       </c>
       <c r="P39" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R39" t="str">
         <v>30</v>
@@ -6681,10 +6681,10 @@
         <v/>
       </c>
       <c r="P40" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R40" t="str">
         <v>30</v>
@@ -6800,10 +6800,10 @@
         <v/>
       </c>
       <c r="P41" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R41" t="str">
         <v>30</v>
@@ -6919,10 +6919,10 @@
         <v/>
       </c>
       <c r="P42" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R42" t="str">
         <v>30</v>
@@ -7038,10 +7038,10 @@
         <v/>
       </c>
       <c r="P43" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R43" t="str">
         <v>30</v>
@@ -7157,10 +7157,10 @@
         <v/>
       </c>
       <c r="P44" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R44" t="str">
         <v>34</v>
@@ -7276,10 +7276,10 @@
         <v/>
       </c>
       <c r="P45" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R45" t="str">
         <v>34</v>
@@ -7395,10 +7395,10 @@
         <v/>
       </c>
       <c r="P46" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R46" t="str">
         <v>34</v>
@@ -7514,10 +7514,10 @@
         <v/>
       </c>
       <c r="P47" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R47" t="str">
         <v>34</v>
@@ -7633,10 +7633,10 @@
         <v/>
       </c>
       <c r="P48" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R48" t="str">
         <v>28</v>
@@ -7752,10 +7752,10 @@
         <v/>
       </c>
       <c r="P49" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R49" t="str">
         <v>28</v>
@@ -7871,10 +7871,10 @@
         <v/>
       </c>
       <c r="P50" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R50" t="str">
         <v>34</v>
@@ -7990,10 +7990,10 @@
         <v/>
       </c>
       <c r="P51" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q51" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R51" t="str">
         <v>34</v>
@@ -8109,10 +8109,10 @@
         <v/>
       </c>
       <c r="P52" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q52" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R52" t="str">
         <v>34</v>
@@ -8228,10 +8228,10 @@
         <v/>
       </c>
       <c r="P53" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q53" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R53" t="str">
         <v>34</v>
@@ -8347,10 +8347,10 @@
         <v/>
       </c>
       <c r="P54" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q54" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R54" t="str">
         <v>30</v>
@@ -8466,10 +8466,10 @@
         <v/>
       </c>
       <c r="P55" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q55" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R55" t="str">
         <v>30</v>
@@ -8585,10 +8585,10 @@
         <v/>
       </c>
       <c r="P56" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q56" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R56" t="str">
         <v>34</v>
@@ -8704,10 +8704,10 @@
         <v/>
       </c>
       <c r="P57" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q57" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R57" t="str">
         <v>34</v>
@@ -8823,10 +8823,10 @@
         <v/>
       </c>
       <c r="P58" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q58" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R58" t="str">
         <v>34</v>
@@ -8942,10 +8942,10 @@
         <v/>
       </c>
       <c r="P59" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q59" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R59" t="str">
         <v>34</v>
@@ -9061,10 +9061,10 @@
         <v/>
       </c>
       <c r="P60" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q60" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R60" t="str">
         <v>34</v>
@@ -9180,10 +9180,10 @@
         <v/>
       </c>
       <c r="P61" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q61" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R61" t="str">
         <v>34</v>
@@ -9299,10 +9299,10 @@
         <v/>
       </c>
       <c r="P62" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q62" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R62" t="str">
         <v>36</v>
@@ -9418,10 +9418,10 @@
         <v/>
       </c>
       <c r="P63" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q63" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R63" t="str">
         <v>36</v>
@@ -9537,10 +9537,10 @@
         <v/>
       </c>
       <c r="P64" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q64" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R64" t="str">
         <v>36</v>
@@ -9656,10 +9656,10 @@
         <v/>
       </c>
       <c r="P65" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q65" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R65" t="str">
         <v>36</v>
@@ -9775,10 +9775,10 @@
         <v/>
       </c>
       <c r="P66" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q66" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R66" t="str">
         <v>36</v>
@@ -9894,10 +9894,10 @@
         <v/>
       </c>
       <c r="P67" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q67" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R67" t="str">
         <v>36</v>
@@ -10013,10 +10013,10 @@
         <v/>
       </c>
       <c r="P68" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q68" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R68" t="str">
         <v>34</v>
@@ -10132,10 +10132,10 @@
         <v/>
       </c>
       <c r="P69" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q69" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R69" t="str">
         <v>34</v>
@@ -10251,10 +10251,10 @@
         <v/>
       </c>
       <c r="P70" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q70" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R70" t="str">
         <v>34</v>
@@ -10370,10 +10370,10 @@
         <v/>
       </c>
       <c r="P71" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q71" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R71" t="str">
         <v>34</v>
@@ -10489,10 +10489,10 @@
         <v/>
       </c>
       <c r="P72" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q72" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R72" t="str">
         <v>28</v>
@@ -10608,10 +10608,10 @@
         <v/>
       </c>
       <c r="P73" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q73" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R73" t="str">
         <v>28</v>
@@ -10727,10 +10727,10 @@
         <v/>
       </c>
       <c r="P74" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q74" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R74" t="str">
         <v/>
@@ -10846,10 +10846,10 @@
         <v/>
       </c>
       <c r="P75" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q75" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R75" t="str">
         <v/>
@@ -10965,10 +10965,10 @@
         <v/>
       </c>
       <c r="P76" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q76" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R76" t="str">
         <v>30</v>
@@ -11084,10 +11084,10 @@
         <v/>
       </c>
       <c r="P77" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q77" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R77" t="str">
         <v>30</v>
@@ -11203,10 +11203,10 @@
         <v/>
       </c>
       <c r="P78" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q78" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R78" t="str">
         <v>30</v>
@@ -11322,10 +11322,10 @@
         <v/>
       </c>
       <c r="P79" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q79" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R79" t="str">
         <v>30</v>
@@ -11441,10 +11441,10 @@
         <v/>
       </c>
       <c r="P80" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R80" t="str">
         <v>34</v>
@@ -11560,10 +11560,10 @@
         <v/>
       </c>
       <c r="P81" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R81" t="str">
         <v>34</v>
@@ -11679,10 +11679,10 @@
         <v/>
       </c>
       <c r="P82" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R82" t="str">
         <v>34</v>
@@ -11798,10 +11798,10 @@
         <v/>
       </c>
       <c r="P83" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R83" t="str">
         <v>34</v>
@@ -11917,10 +11917,10 @@
         <v/>
       </c>
       <c r="P84" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R84" t="str">
         <v>34</v>
@@ -12036,10 +12036,10 @@
         <v/>
       </c>
       <c r="P85" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R85" t="str">
         <v>34</v>
@@ -12155,10 +12155,10 @@
         <v/>
       </c>
       <c r="P86" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R86" t="str">
         <v>34</v>
@@ -12274,10 +12274,10 @@
         <v/>
       </c>
       <c r="P87" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R87" t="str">
         <v>34</v>
@@ -12393,10 +12393,10 @@
         <v/>
       </c>
       <c r="P88" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R88" t="str">
         <v>30</v>
@@ -12512,10 +12512,10 @@
         <v/>
       </c>
       <c r="P89" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R89" t="str">
         <v>30</v>
@@ -12631,10 +12631,10 @@
         <v/>
       </c>
       <c r="P90" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R90" t="str">
         <v>32</v>
@@ -12750,10 +12750,10 @@
         <v/>
       </c>
       <c r="P91" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R91" t="str">
         <v>32</v>
@@ -12869,10 +12869,10 @@
         <v/>
       </c>
       <c r="P92" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R92" t="str">
         <v>34</v>
@@ -12988,10 +12988,10 @@
         <v/>
       </c>
       <c r="P93" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q93" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R93" t="str">
         <v>34</v>
@@ -13107,10 +13107,10 @@
         <v/>
       </c>
       <c r="P94" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q94" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R94" t="str">
         <v>36</v>
@@ -13226,10 +13226,10 @@
         <v/>
       </c>
       <c r="P95" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R95" t="str">
         <v>36</v>
@@ -13345,10 +13345,10 @@
         <v/>
       </c>
       <c r="P96" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q96" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R96" t="str">
         <v>43</v>
@@ -13464,10 +13464,10 @@
         <v/>
       </c>
       <c r="P97" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R97" t="str">
         <v>43</v>
@@ -13583,10 +13583,10 @@
         <v/>
       </c>
       <c r="P98" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R98" t="str">
         <v>43</v>
@@ -13702,10 +13702,10 @@
         <v/>
       </c>
       <c r="P99" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R99" t="str">
         <v>43</v>
@@ -13821,10 +13821,10 @@
         <v/>
       </c>
       <c r="P100" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R100" t="str">
         <v>43</v>
@@ -13940,10 +13940,10 @@
         <v/>
       </c>
       <c r="P101" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R101" t="str">
         <v>43</v>
@@ -14059,10 +14059,10 @@
         <v/>
       </c>
       <c r="P102" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R102" t="str">
         <v>43</v>
@@ -14178,10 +14178,10 @@
         <v/>
       </c>
       <c r="P103" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R103" t="str">
         <v>43</v>
@@ -14297,10 +14297,10 @@
         <v/>
       </c>
       <c r="P104" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R104" t="str">
         <v>43</v>
@@ -14416,10 +14416,10 @@
         <v/>
       </c>
       <c r="P105" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R105" t="str">
         <v>43</v>
@@ -14535,10 +14535,10 @@
         <v/>
       </c>
       <c r="P106" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q106" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R106" t="str">
         <v>43</v>
@@ -14654,10 +14654,10 @@
         <v/>
       </c>
       <c r="P107" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R107" t="str">
         <v>43</v>
@@ -14773,10 +14773,10 @@
         <v/>
       </c>
       <c r="P108" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R108" t="str">
         <v>43</v>
@@ -14892,10 +14892,10 @@
         <v/>
       </c>
       <c r="P109" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R109" t="str">
         <v>43</v>
@@ -15011,10 +15011,10 @@
         <v/>
       </c>
       <c r="P110" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q110" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R110" t="str">
         <v>32</v>
@@ -15130,10 +15130,10 @@
         <v/>
       </c>
       <c r="P111" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R111" t="str">
         <v>32</v>
@@ -15249,10 +15249,10 @@
         <v/>
       </c>
       <c r="P112" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R112" t="str">
         <v>32</v>
@@ -15368,10 +15368,10 @@
         <v/>
       </c>
       <c r="P113" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q113" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R113" t="str">
         <v>32</v>
@@ -15487,10 +15487,10 @@
         <v/>
       </c>
       <c r="P114" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q114" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R114" t="str">
         <v>32</v>
@@ -15606,10 +15606,10 @@
         <v/>
       </c>
       <c r="P115" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q115" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R115" t="str">
         <v>32</v>
@@ -15725,10 +15725,10 @@
         <v/>
       </c>
       <c r="P116" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R116" t="str">
         <v>32</v>
@@ -15844,10 +15844,10 @@
         <v/>
       </c>
       <c r="P117" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R117" t="str">
         <v>32</v>
@@ -15963,10 +15963,10 @@
         <v/>
       </c>
       <c r="P118" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R118" t="str">
         <v>30</v>
@@ -16082,10 +16082,10 @@
         <v/>
       </c>
       <c r="P119" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R119" t="str">
         <v>30</v>
@@ -16201,10 +16201,10 @@
         <v/>
       </c>
       <c r="P120" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q120" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R120" t="str">
         <v>38</v>
@@ -16320,10 +16320,10 @@
         <v/>
       </c>
       <c r="P121" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q121" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R121" t="str">
         <v>38</v>
@@ -16439,10 +16439,10 @@
         <v/>
       </c>
       <c r="P122" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q122" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R122" t="str">
         <v>38</v>
@@ -16558,10 +16558,10 @@
         <v/>
       </c>
       <c r="P123" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q123" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R123" t="str">
         <v>38</v>
@@ -16677,10 +16677,10 @@
         <v/>
       </c>
       <c r="P124" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q124" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R124" t="str">
         <v>32</v>
@@ -16796,10 +16796,10 @@
         <v/>
       </c>
       <c r="P125" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q125" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R125" t="str">
         <v>32</v>
@@ -16915,10 +16915,10 @@
         <v/>
       </c>
       <c r="P126" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q126" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R126" t="str">
         <v>32</v>
@@ -17034,10 +17034,10 @@
         <v/>
       </c>
       <c r="P127" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q127" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R127" t="str">
         <v>32</v>
@@ -17153,10 +17153,10 @@
         <v/>
       </c>
       <c r="P128" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q128" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R128" t="str">
         <v>32</v>
@@ -17272,10 +17272,10 @@
         <v/>
       </c>
       <c r="P129" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q129" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R129" t="str">
         <v>32</v>
@@ -17391,10 +17391,10 @@
         <v/>
       </c>
       <c r="P130" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q130" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R130" t="str">
         <v>34</v>
@@ -17510,10 +17510,10 @@
         <v/>
       </c>
       <c r="P131" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q131" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R131" t="str">
         <v>34</v>
@@ -17629,10 +17629,10 @@
         <v/>
       </c>
       <c r="P132" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q132" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R132" t="str">
         <v>34</v>
@@ -17748,10 +17748,10 @@
         <v/>
       </c>
       <c r="P133" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q133" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R133" t="str">
         <v>34</v>
@@ -17867,10 +17867,10 @@
         <v/>
       </c>
       <c r="P134" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q134" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R134" t="str">
         <v>34</v>
@@ -17986,10 +17986,10 @@
         <v/>
       </c>
       <c r="P135" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q135" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R135" t="str">
         <v>34</v>
@@ -18105,10 +18105,10 @@
         <v/>
       </c>
       <c r="P136" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q136" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R136" t="str">
         <v>32</v>
@@ -18224,10 +18224,10 @@
         <v/>
       </c>
       <c r="P137" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q137" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R137" t="str">
         <v>32</v>
@@ -18343,10 +18343,10 @@
         <v/>
       </c>
       <c r="P138" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q138" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R138" t="str">
         <v>32</v>
@@ -18462,10 +18462,10 @@
         <v/>
       </c>
       <c r="P139" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q139" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R139" t="str">
         <v>32</v>
@@ -18581,10 +18581,10 @@
         <v/>
       </c>
       <c r="P140" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q140" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R140" t="str">
         <v>32</v>
@@ -18700,10 +18700,10 @@
         <v/>
       </c>
       <c r="P141" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q141" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R141" t="str">
         <v>32</v>
@@ -18819,10 +18819,10 @@
         <v/>
       </c>
       <c r="P142" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="Q142" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T04:52:05.959Z</v>
       </c>
       <c r="R142" t="str">
         <v>32</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
@@ -467,7 +467,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>baitcasting</v>
@@ -476,10 +476,10 @@
         <v>images/daiwa_reels/IM_Z_リミットブレイカー_TW_HD-C_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -518,7 +518,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>baitcasting</v>
@@ -527,10 +527,10 @@
         <v>images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -569,7 +569,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v>baitcasting</v>
@@ -578,10 +578,10 @@
         <v>images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -621,7 +621,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>baitcasting</v>
@@ -630,10 +630,10 @@
         <v>images/daiwa_reels/スティーズ_リミテッド_CT_SV_TW_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -672,7 +672,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>baitcasting</v>
@@ -681,10 +681,10 @@
         <v>images/daiwa_reels/スティーズ_SV_ライト_TW_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -721,7 +721,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>baitcasting</v>
@@ -730,10 +730,10 @@
         <v>images/daiwa_reels/スティーズ_SV_TW100_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>baitcasting</v>
@@ -781,10 +781,10 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -823,7 +823,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v>baitcasting</v>
@@ -832,10 +832,10 @@
         <v>images/daiwa_reels/リョウガ_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -876,7 +876,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v>baitcasting</v>
@@ -885,10 +885,10 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -925,7 +925,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>baitcasting</v>
@@ -934,10 +934,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_tw_hd_22/__icsFiles/afieldfile/2022/04/08/main.jpg?rev=dd8848fe936e4b268b8bdb9e4b33a4df</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>baitcasting</v>
@@ -986,10 +986,10 @@
         <v>images/daiwa_reels/月下美人_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1029,7 +1029,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>baitcasting</v>
@@ -1038,10 +1038,10 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1079,7 +1079,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>baitcasting</v>
@@ -1088,10 +1088,10 @@
         <v>images/daiwa_reels/シルバーウルフ_CT_SV_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>baitcasting</v>
@@ -1141,10 +1141,10 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>baitcasting</v>
@@ -1190,10 +1190,10 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1232,7 +1232,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>baitcasting</v>
@@ -1241,10 +1241,10 @@
         <v>images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1285,7 +1285,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>baitcasting</v>
@@ -1294,10 +1294,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/salt_rl/silverwolf_sv_tw/__icsFiles/artimage/2022/04/01/c_041110017/main_tx_im01_1.jpg?rev=6d195f85744643bda6ef194759f4c436</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>baitcasting</v>
@@ -1343,10 +1343,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/silvercreek_air_tw_sc/__icsFiles/artimage/2022/03/29/c_041101086/main_tx_im01_3.jpg?rev=d0db4f46700344e7893e0f732daf59a2</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1385,7 +1385,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>baitcasting</v>
@@ -1394,10 +1394,10 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>baitcasting</v>
@@ -1446,10 +1446,10 @@
         <v>images/daiwa_reels/アルファスBF_TW_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v>baitcasting</v>
@@ -1499,10 +1499,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_sv_tw21/__icsFiles/artimage/2022/05/02/c_041101076/main_bg02_1.jpg?rev=eb0a7bf7b3584f528da16f4584f37003</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>baitcasting</v>
@@ -1550,10 +1550,10 @@
         <v>images/daiwa_reels/ソルティスト_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1593,7 +1593,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H24" t="str">
         <v>baitcasting</v>
@@ -1602,10 +1602,10 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1644,7 +1644,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H25" t="str">
         <v>baitcasting</v>
@@ -1653,10 +1653,10 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>baitcasting</v>
@@ -1702,10 +1702,10 @@
         <v>images/daiwa_reels/タトゥーラ_BF_TW_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1746,7 +1746,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v>baitcasting</v>
@@ -1755,10 +1755,10 @@
         <v>images/daiwa_reels/タトゥーラ_TW_200_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1800,7 +1800,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H28" t="str">
         <v>baitcasting</v>
@@ -1809,10 +1809,10 @@
         <v>images/daiwa_reels/タトゥーラ_SV_TW_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1852,7 +1852,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>baitcasting</v>
@@ -1861,10 +1861,10 @@
         <v>images/daiwa_reels/タトゥーラ_TW_100_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>baitcasting</v>
@@ -1913,10 +1913,10 @@
         <v>images/daiwa_reels/バス__X__100_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>baitcasting</v>
@@ -1962,10 +1962,10 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -2159,10 +2159,10 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R2" t="str">
         <v>38</v>
@@ -2278,10 +2278,10 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R3" t="str">
         <v>38</v>
@@ -2397,10 +2397,10 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R4" t="str">
         <v>38</v>
@@ -2516,10 +2516,10 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R5" t="str">
         <v>38</v>
@@ -2635,10 +2635,10 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R6" t="str">
         <v>38</v>
@@ -2754,10 +2754,10 @@
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R7" t="str">
         <v>38</v>
@@ -2873,10 +2873,10 @@
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R8" t="str">
         <v>34</v>
@@ -2992,10 +2992,10 @@
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R9" t="str">
         <v>34</v>
@@ -3111,10 +3111,10 @@
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R10" t="str">
         <v>34</v>
@@ -3230,10 +3230,10 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R11" t="str">
         <v>34</v>
@@ -3349,10 +3349,10 @@
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R12" t="str">
         <v>34</v>
@@ -3468,10 +3468,10 @@
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R13" t="str">
         <v>34</v>
@@ -3587,10 +3587,10 @@
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R14" t="str">
         <v>φ30</v>
@@ -3706,10 +3706,10 @@
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R15" t="str">
         <v>φ30</v>
@@ -3825,10 +3825,10 @@
         <v/>
       </c>
       <c r="P16" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R16" t="str">
         <v>32</v>
@@ -3944,10 +3944,10 @@
         <v/>
       </c>
       <c r="P17" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R17" t="str">
         <v>32</v>
@@ -4063,10 +4063,10 @@
         <v/>
       </c>
       <c r="P18" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R18" t="str">
         <v>32</v>
@@ -4182,10 +4182,10 @@
         <v/>
       </c>
       <c r="P19" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R19" t="str">
         <v>32</v>
@@ -4301,10 +4301,10 @@
         <v/>
       </c>
       <c r="P20" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R20" t="str">
         <v>32</v>
@@ -4420,10 +4420,10 @@
         <v/>
       </c>
       <c r="P21" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R21" t="str">
         <v>32</v>
@@ -4539,10 +4539,10 @@
         <v/>
       </c>
       <c r="P22" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R22" t="str">
         <v>32</v>
@@ -4658,10 +4658,10 @@
         <v/>
       </c>
       <c r="P23" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R23" t="str">
         <v>32</v>
@@ -4777,10 +4777,10 @@
         <v/>
       </c>
       <c r="P24" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R24" t="str">
         <v>32</v>
@@ -4896,10 +4896,10 @@
         <v/>
       </c>
       <c r="P25" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R25" t="str">
         <v>32</v>
@@ -5015,10 +5015,10 @@
         <v/>
       </c>
       <c r="P26" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R26" t="str">
         <v>28</v>
@@ -5134,10 +5134,10 @@
         <v/>
       </c>
       <c r="P27" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R27" t="str">
         <v>28</v>
@@ -5253,10 +5253,10 @@
         <v/>
       </c>
       <c r="P28" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R28" t="str">
         <v>28</v>
@@ -5372,10 +5372,10 @@
         <v/>
       </c>
       <c r="P29" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R29" t="str">
         <v>28</v>
@@ -5491,10 +5491,10 @@
         <v/>
       </c>
       <c r="P30" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R30" t="str">
         <v>34</v>
@@ -5610,10 +5610,10 @@
         <v/>
       </c>
       <c r="P31" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R31" t="str">
         <v>34</v>
@@ -5729,10 +5729,10 @@
         <v/>
       </c>
       <c r="P32" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R32" t="str">
         <v>34</v>
@@ -5848,10 +5848,10 @@
         <v/>
       </c>
       <c r="P33" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R33" t="str">
         <v>34</v>
@@ -5967,10 +5967,10 @@
         <v/>
       </c>
       <c r="P34" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R34" t="str">
         <v>36</v>
@@ -6086,10 +6086,10 @@
         <v/>
       </c>
       <c r="P35" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R35" t="str">
         <v>36</v>
@@ -6205,10 +6205,10 @@
         <v/>
       </c>
       <c r="P36" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R36" t="str">
         <v>36</v>
@@ -6324,10 +6324,10 @@
         <v/>
       </c>
       <c r="P37" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R37" t="str">
         <v>36</v>
@@ -6443,10 +6443,10 @@
         <v/>
       </c>
       <c r="P38" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R38" t="str">
         <v>30</v>
@@ -6562,10 +6562,10 @@
         <v/>
       </c>
       <c r="P39" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R39" t="str">
         <v>30</v>
@@ -6681,10 +6681,10 @@
         <v/>
       </c>
       <c r="P40" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R40" t="str">
         <v>30</v>
@@ -6800,10 +6800,10 @@
         <v/>
       </c>
       <c r="P41" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R41" t="str">
         <v>30</v>
@@ -6919,10 +6919,10 @@
         <v/>
       </c>
       <c r="P42" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R42" t="str">
         <v>30</v>
@@ -7038,10 +7038,10 @@
         <v/>
       </c>
       <c r="P43" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R43" t="str">
         <v>30</v>
@@ -7157,10 +7157,10 @@
         <v/>
       </c>
       <c r="P44" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R44" t="str">
         <v>34</v>
@@ -7276,10 +7276,10 @@
         <v/>
       </c>
       <c r="P45" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R45" t="str">
         <v>34</v>
@@ -7395,10 +7395,10 @@
         <v/>
       </c>
       <c r="P46" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R46" t="str">
         <v>34</v>
@@ -7514,10 +7514,10 @@
         <v/>
       </c>
       <c r="P47" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R47" t="str">
         <v>34</v>
@@ -7633,10 +7633,10 @@
         <v/>
       </c>
       <c r="P48" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R48" t="str">
         <v>28</v>
@@ -7752,10 +7752,10 @@
         <v/>
       </c>
       <c r="P49" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R49" t="str">
         <v>28</v>
@@ -7871,10 +7871,10 @@
         <v/>
       </c>
       <c r="P50" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R50" t="str">
         <v>34</v>
@@ -7990,10 +7990,10 @@
         <v/>
       </c>
       <c r="P51" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q51" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R51" t="str">
         <v>34</v>
@@ -8109,10 +8109,10 @@
         <v/>
       </c>
       <c r="P52" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q52" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R52" t="str">
         <v>34</v>
@@ -8228,10 +8228,10 @@
         <v/>
       </c>
       <c r="P53" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q53" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R53" t="str">
         <v>34</v>
@@ -8347,10 +8347,10 @@
         <v/>
       </c>
       <c r="P54" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q54" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R54" t="str">
         <v>30</v>
@@ -8466,10 +8466,10 @@
         <v/>
       </c>
       <c r="P55" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q55" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R55" t="str">
         <v>30</v>
@@ -8585,10 +8585,10 @@
         <v/>
       </c>
       <c r="P56" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q56" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R56" t="str">
         <v>34</v>
@@ -8704,10 +8704,10 @@
         <v/>
       </c>
       <c r="P57" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q57" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R57" t="str">
         <v>34</v>
@@ -8823,10 +8823,10 @@
         <v/>
       </c>
       <c r="P58" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q58" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R58" t="str">
         <v>34</v>
@@ -8942,10 +8942,10 @@
         <v/>
       </c>
       <c r="P59" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q59" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R59" t="str">
         <v>34</v>
@@ -9061,10 +9061,10 @@
         <v/>
       </c>
       <c r="P60" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q60" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R60" t="str">
         <v>34</v>
@@ -9180,10 +9180,10 @@
         <v/>
       </c>
       <c r="P61" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q61" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R61" t="str">
         <v>34</v>
@@ -9299,10 +9299,10 @@
         <v/>
       </c>
       <c r="P62" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q62" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R62" t="str">
         <v>36</v>
@@ -9418,10 +9418,10 @@
         <v/>
       </c>
       <c r="P63" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q63" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R63" t="str">
         <v>36</v>
@@ -9537,10 +9537,10 @@
         <v/>
       </c>
       <c r="P64" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q64" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R64" t="str">
         <v>36</v>
@@ -9656,10 +9656,10 @@
         <v/>
       </c>
       <c r="P65" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q65" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R65" t="str">
         <v>36</v>
@@ -9775,10 +9775,10 @@
         <v/>
       </c>
       <c r="P66" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q66" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R66" t="str">
         <v>36</v>
@@ -9894,10 +9894,10 @@
         <v/>
       </c>
       <c r="P67" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q67" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R67" t="str">
         <v>36</v>
@@ -10013,10 +10013,10 @@
         <v/>
       </c>
       <c r="P68" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q68" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R68" t="str">
         <v>34</v>
@@ -10132,10 +10132,10 @@
         <v/>
       </c>
       <c r="P69" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q69" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R69" t="str">
         <v>34</v>
@@ -10251,10 +10251,10 @@
         <v/>
       </c>
       <c r="P70" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q70" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R70" t="str">
         <v>34</v>
@@ -10370,10 +10370,10 @@
         <v/>
       </c>
       <c r="P71" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q71" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R71" t="str">
         <v>34</v>
@@ -10489,10 +10489,10 @@
         <v/>
       </c>
       <c r="P72" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q72" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R72" t="str">
         <v>28</v>
@@ -10608,10 +10608,10 @@
         <v/>
       </c>
       <c r="P73" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q73" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R73" t="str">
         <v>28</v>
@@ -10727,10 +10727,10 @@
         <v/>
       </c>
       <c r="P74" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q74" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R74" t="str">
         <v/>
@@ -10846,10 +10846,10 @@
         <v/>
       </c>
       <c r="P75" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q75" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R75" t="str">
         <v/>
@@ -10965,10 +10965,10 @@
         <v/>
       </c>
       <c r="P76" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q76" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R76" t="str">
         <v>30</v>
@@ -11084,10 +11084,10 @@
         <v/>
       </c>
       <c r="P77" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q77" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R77" t="str">
         <v>30</v>
@@ -11203,10 +11203,10 @@
         <v/>
       </c>
       <c r="P78" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q78" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R78" t="str">
         <v>30</v>
@@ -11322,10 +11322,10 @@
         <v/>
       </c>
       <c r="P79" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q79" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R79" t="str">
         <v>30</v>
@@ -11441,10 +11441,10 @@
         <v/>
       </c>
       <c r="P80" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R80" t="str">
         <v>34</v>
@@ -11560,10 +11560,10 @@
         <v/>
       </c>
       <c r="P81" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R81" t="str">
         <v>34</v>
@@ -11679,10 +11679,10 @@
         <v/>
       </c>
       <c r="P82" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R82" t="str">
         <v>34</v>
@@ -11798,10 +11798,10 @@
         <v/>
       </c>
       <c r="P83" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R83" t="str">
         <v>34</v>
@@ -11917,10 +11917,10 @@
         <v/>
       </c>
       <c r="P84" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R84" t="str">
         <v>34</v>
@@ -12036,10 +12036,10 @@
         <v/>
       </c>
       <c r="P85" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R85" t="str">
         <v>34</v>
@@ -12155,10 +12155,10 @@
         <v/>
       </c>
       <c r="P86" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R86" t="str">
         <v>34</v>
@@ -12274,10 +12274,10 @@
         <v/>
       </c>
       <c r="P87" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R87" t="str">
         <v>34</v>
@@ -12393,10 +12393,10 @@
         <v/>
       </c>
       <c r="P88" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R88" t="str">
         <v>30</v>
@@ -12512,10 +12512,10 @@
         <v/>
       </c>
       <c r="P89" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R89" t="str">
         <v>30</v>
@@ -12631,10 +12631,10 @@
         <v/>
       </c>
       <c r="P90" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R90" t="str">
         <v>32</v>
@@ -12750,10 +12750,10 @@
         <v/>
       </c>
       <c r="P91" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R91" t="str">
         <v>32</v>
@@ -12869,10 +12869,10 @@
         <v/>
       </c>
       <c r="P92" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R92" t="str">
         <v>34</v>
@@ -12988,10 +12988,10 @@
         <v/>
       </c>
       <c r="P93" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q93" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R93" t="str">
         <v>34</v>
@@ -13107,10 +13107,10 @@
         <v/>
       </c>
       <c r="P94" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q94" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R94" t="str">
         <v>36</v>
@@ -13226,10 +13226,10 @@
         <v/>
       </c>
       <c r="P95" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R95" t="str">
         <v>36</v>
@@ -13345,10 +13345,10 @@
         <v/>
       </c>
       <c r="P96" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q96" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R96" t="str">
         <v>43</v>
@@ -13464,10 +13464,10 @@
         <v/>
       </c>
       <c r="P97" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R97" t="str">
         <v>43</v>
@@ -13583,10 +13583,10 @@
         <v/>
       </c>
       <c r="P98" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R98" t="str">
         <v>43</v>
@@ -13702,10 +13702,10 @@
         <v/>
       </c>
       <c r="P99" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R99" t="str">
         <v>43</v>
@@ -13821,10 +13821,10 @@
         <v/>
       </c>
       <c r="P100" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R100" t="str">
         <v>43</v>
@@ -13940,10 +13940,10 @@
         <v/>
       </c>
       <c r="P101" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R101" t="str">
         <v>43</v>
@@ -14059,10 +14059,10 @@
         <v/>
       </c>
       <c r="P102" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R102" t="str">
         <v>43</v>
@@ -14178,10 +14178,10 @@
         <v/>
       </c>
       <c r="P103" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R103" t="str">
         <v>43</v>
@@ -14297,10 +14297,10 @@
         <v/>
       </c>
       <c r="P104" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R104" t="str">
         <v>43</v>
@@ -14416,10 +14416,10 @@
         <v/>
       </c>
       <c r="P105" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R105" t="str">
         <v>43</v>
@@ -14535,10 +14535,10 @@
         <v/>
       </c>
       <c r="P106" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q106" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R106" t="str">
         <v>43</v>
@@ -14654,10 +14654,10 @@
         <v/>
       </c>
       <c r="P107" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R107" t="str">
         <v>43</v>
@@ -14773,10 +14773,10 @@
         <v/>
       </c>
       <c r="P108" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R108" t="str">
         <v>43</v>
@@ -14892,10 +14892,10 @@
         <v/>
       </c>
       <c r="P109" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R109" t="str">
         <v>43</v>
@@ -15011,10 +15011,10 @@
         <v/>
       </c>
       <c r="P110" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q110" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R110" t="str">
         <v>32</v>
@@ -15130,10 +15130,10 @@
         <v/>
       </c>
       <c r="P111" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R111" t="str">
         <v>32</v>
@@ -15249,10 +15249,10 @@
         <v/>
       </c>
       <c r="P112" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R112" t="str">
         <v>32</v>
@@ -15368,10 +15368,10 @@
         <v/>
       </c>
       <c r="P113" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q113" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R113" t="str">
         <v>32</v>
@@ -15487,10 +15487,10 @@
         <v/>
       </c>
       <c r="P114" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q114" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R114" t="str">
         <v>32</v>
@@ -15606,10 +15606,10 @@
         <v/>
       </c>
       <c r="P115" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q115" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R115" t="str">
         <v>32</v>
@@ -15725,10 +15725,10 @@
         <v/>
       </c>
       <c r="P116" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R116" t="str">
         <v>32</v>
@@ -15844,10 +15844,10 @@
         <v/>
       </c>
       <c r="P117" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R117" t="str">
         <v>32</v>
@@ -15963,10 +15963,10 @@
         <v/>
       </c>
       <c r="P118" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R118" t="str">
         <v>30</v>
@@ -16082,10 +16082,10 @@
         <v/>
       </c>
       <c r="P119" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R119" t="str">
         <v>30</v>
@@ -16201,10 +16201,10 @@
         <v/>
       </c>
       <c r="P120" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q120" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R120" t="str">
         <v>38</v>
@@ -16320,10 +16320,10 @@
         <v/>
       </c>
       <c r="P121" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q121" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R121" t="str">
         <v>38</v>
@@ -16439,10 +16439,10 @@
         <v/>
       </c>
       <c r="P122" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q122" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R122" t="str">
         <v>38</v>
@@ -16558,10 +16558,10 @@
         <v/>
       </c>
       <c r="P123" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q123" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R123" t="str">
         <v>38</v>
@@ -16677,10 +16677,10 @@
         <v/>
       </c>
       <c r="P124" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q124" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R124" t="str">
         <v>32</v>
@@ -16796,10 +16796,10 @@
         <v/>
       </c>
       <c r="P125" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q125" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R125" t="str">
         <v>32</v>
@@ -16915,10 +16915,10 @@
         <v/>
       </c>
       <c r="P126" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q126" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R126" t="str">
         <v>32</v>
@@ -17034,10 +17034,10 @@
         <v/>
       </c>
       <c r="P127" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q127" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R127" t="str">
         <v>32</v>
@@ -17153,10 +17153,10 @@
         <v/>
       </c>
       <c r="P128" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q128" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R128" t="str">
         <v>32</v>
@@ -17272,10 +17272,10 @@
         <v/>
       </c>
       <c r="P129" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q129" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R129" t="str">
         <v>32</v>
@@ -17391,10 +17391,10 @@
         <v/>
       </c>
       <c r="P130" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q130" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R130" t="str">
         <v>34</v>
@@ -17510,10 +17510,10 @@
         <v/>
       </c>
       <c r="P131" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q131" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R131" t="str">
         <v>34</v>
@@ -17629,10 +17629,10 @@
         <v/>
       </c>
       <c r="P132" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q132" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R132" t="str">
         <v>34</v>
@@ -17748,10 +17748,10 @@
         <v/>
       </c>
       <c r="P133" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q133" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R133" t="str">
         <v>34</v>
@@ -17867,10 +17867,10 @@
         <v/>
       </c>
       <c r="P134" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q134" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R134" t="str">
         <v>34</v>
@@ -17986,10 +17986,10 @@
         <v/>
       </c>
       <c r="P135" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q135" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R135" t="str">
         <v>34</v>
@@ -18105,10 +18105,10 @@
         <v/>
       </c>
       <c r="P136" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q136" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R136" t="str">
         <v>32</v>
@@ -18224,10 +18224,10 @@
         <v/>
       </c>
       <c r="P137" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q137" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R137" t="str">
         <v>32</v>
@@ -18343,10 +18343,10 @@
         <v/>
       </c>
       <c r="P138" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q138" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R138" t="str">
         <v>32</v>
@@ -18462,10 +18462,10 @@
         <v/>
       </c>
       <c r="P139" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q139" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R139" t="str">
         <v>32</v>
@@ -18581,10 +18581,10 @@
         <v/>
       </c>
       <c r="P140" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q140" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R140" t="str">
         <v>32</v>
@@ -18700,10 +18700,10 @@
         <v/>
       </c>
       <c r="P141" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q141" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R141" t="str">
         <v>32</v>
@@ -18819,10 +18819,10 @@
         <v/>
       </c>
       <c r="P142" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="Q142" t="str">
-        <v>2026-04-09T04:52:05.959Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="R142" t="str">
         <v>32</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
@@ -1991,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM142"/>
+  <dimension ref="A1:AN142"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2111,6 +2111,9 @@
       <c r="AM1" t="str">
         <v>MAX_DURABILITY</v>
       </c>
+      <c r="AN1" t="str">
+        <v>type</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2230,6 +2233,9 @@
       <c r="AM2" t="str">
         <v/>
       </c>
+      <c r="AN2" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -2349,6 +2355,9 @@
       <c r="AM3" t="str">
         <v/>
       </c>
+      <c r="AN3" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2468,6 +2477,9 @@
       <c r="AM4" t="str">
         <v/>
       </c>
+      <c r="AN4" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2587,6 +2599,9 @@
       <c r="AM5" t="str">
         <v/>
       </c>
+      <c r="AN5" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2706,6 +2721,9 @@
       <c r="AM6" t="str">
         <v/>
       </c>
+      <c r="AN6" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -2825,6 +2843,9 @@
       <c r="AM7" t="str">
         <v/>
       </c>
+      <c r="AN7" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -2944,6 +2965,9 @@
       <c r="AM8" t="str">
         <v/>
       </c>
+      <c r="AN8" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -3063,6 +3087,9 @@
       <c r="AM9" t="str">
         <v/>
       </c>
+      <c r="AN9" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -3182,6 +3209,9 @@
       <c r="AM10" t="str">
         <v/>
       </c>
+      <c r="AN10" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -3301,6 +3331,9 @@
       <c r="AM11" t="str">
         <v/>
       </c>
+      <c r="AN11" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -3420,6 +3453,9 @@
       <c r="AM12" t="str">
         <v/>
       </c>
+      <c r="AN12" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -3539,6 +3575,9 @@
       <c r="AM13" t="str">
         <v/>
       </c>
+      <c r="AN13" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -3658,6 +3697,9 @@
       <c r="AM14" t="str">
         <v/>
       </c>
+      <c r="AN14" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -3777,6 +3819,9 @@
       <c r="AM15" t="str">
         <v/>
       </c>
+      <c r="AN15" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -3896,6 +3941,9 @@
       <c r="AM16" t="str">
         <v/>
       </c>
+      <c r="AN16" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -4015,6 +4063,9 @@
       <c r="AM17" t="str">
         <v/>
       </c>
+      <c r="AN17" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -4134,6 +4185,9 @@
       <c r="AM18" t="str">
         <v/>
       </c>
+      <c r="AN18" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -4253,6 +4307,9 @@
       <c r="AM19" t="str">
         <v/>
       </c>
+      <c r="AN19" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -4372,6 +4429,9 @@
       <c r="AM20" t="str">
         <v/>
       </c>
+      <c r="AN20" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -4491,6 +4551,9 @@
       <c r="AM21" t="str">
         <v/>
       </c>
+      <c r="AN21" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -4610,6 +4673,9 @@
       <c r="AM22" t="str">
         <v/>
       </c>
+      <c r="AN22" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -4729,6 +4795,9 @@
       <c r="AM23" t="str">
         <v/>
       </c>
+      <c r="AN23" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -4848,6 +4917,9 @@
       <c r="AM24" t="str">
         <v/>
       </c>
+      <c r="AN24" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -4967,6 +5039,9 @@
       <c r="AM25" t="str">
         <v/>
       </c>
+      <c r="AN25" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -5086,6 +5161,9 @@
       <c r="AM26" t="str">
         <v/>
       </c>
+      <c r="AN26" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -5205,6 +5283,9 @@
       <c r="AM27" t="str">
         <v/>
       </c>
+      <c r="AN27" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -5324,6 +5405,9 @@
       <c r="AM28" t="str">
         <v/>
       </c>
+      <c r="AN28" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -5443,6 +5527,9 @@
       <c r="AM29" t="str">
         <v/>
       </c>
+      <c r="AN29" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -5562,6 +5649,9 @@
       <c r="AM30" t="str">
         <v/>
       </c>
+      <c r="AN30" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -5681,6 +5771,9 @@
       <c r="AM31" t="str">
         <v/>
       </c>
+      <c r="AN31" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -5800,6 +5893,9 @@
       <c r="AM32" t="str">
         <v/>
       </c>
+      <c r="AN32" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -5919,6 +6015,9 @@
       <c r="AM33" t="str">
         <v/>
       </c>
+      <c r="AN33" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -6038,6 +6137,9 @@
       <c r="AM34" t="str">
         <v/>
       </c>
+      <c r="AN34" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -6157,6 +6259,9 @@
       <c r="AM35" t="str">
         <v/>
       </c>
+      <c r="AN35" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -6276,6 +6381,9 @@
       <c r="AM36" t="str">
         <v/>
       </c>
+      <c r="AN36" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -6395,6 +6503,9 @@
       <c r="AM37" t="str">
         <v/>
       </c>
+      <c r="AN37" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -6514,6 +6625,9 @@
       <c r="AM38" t="str">
         <v/>
       </c>
+      <c r="AN38" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -6633,6 +6747,9 @@
       <c r="AM39" t="str">
         <v/>
       </c>
+      <c r="AN39" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -6752,6 +6869,9 @@
       <c r="AM40" t="str">
         <v/>
       </c>
+      <c r="AN40" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -6871,6 +6991,9 @@
       <c r="AM41" t="str">
         <v/>
       </c>
+      <c r="AN41" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -6990,6 +7113,9 @@
       <c r="AM42" t="str">
         <v/>
       </c>
+      <c r="AN42" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -7109,6 +7235,9 @@
       <c r="AM43" t="str">
         <v/>
       </c>
+      <c r="AN43" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -7228,6 +7357,9 @@
       <c r="AM44" t="str">
         <v/>
       </c>
+      <c r="AN44" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -7347,6 +7479,9 @@
       <c r="AM45" t="str">
         <v/>
       </c>
+      <c r="AN45" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -7466,6 +7601,9 @@
       <c r="AM46" t="str">
         <v/>
       </c>
+      <c r="AN46" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -7585,6 +7723,9 @@
       <c r="AM47" t="str">
         <v/>
       </c>
+      <c r="AN47" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -7704,6 +7845,9 @@
       <c r="AM48" t="str">
         <v/>
       </c>
+      <c r="AN48" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -7823,6 +7967,9 @@
       <c r="AM49" t="str">
         <v/>
       </c>
+      <c r="AN49" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -7942,6 +8089,9 @@
       <c r="AM50" t="str">
         <v/>
       </c>
+      <c r="AN50" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -8061,6 +8211,9 @@
       <c r="AM51" t="str">
         <v/>
       </c>
+      <c r="AN51" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -8180,6 +8333,9 @@
       <c r="AM52" t="str">
         <v/>
       </c>
+      <c r="AN52" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -8299,6 +8455,9 @@
       <c r="AM53" t="str">
         <v/>
       </c>
+      <c r="AN53" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -8418,6 +8577,9 @@
       <c r="AM54" t="str">
         <v/>
       </c>
+      <c r="AN54" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -8537,6 +8699,9 @@
       <c r="AM55" t="str">
         <v/>
       </c>
+      <c r="AN55" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -8656,6 +8821,9 @@
       <c r="AM56" t="str">
         <v/>
       </c>
+      <c r="AN56" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -8775,6 +8943,9 @@
       <c r="AM57" t="str">
         <v/>
       </c>
+      <c r="AN57" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -8894,6 +9065,9 @@
       <c r="AM58" t="str">
         <v/>
       </c>
+      <c r="AN58" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -9013,6 +9187,9 @@
       <c r="AM59" t="str">
         <v/>
       </c>
+      <c r="AN59" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -9132,6 +9309,9 @@
       <c r="AM60" t="str">
         <v/>
       </c>
+      <c r="AN60" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -9251,6 +9431,9 @@
       <c r="AM61" t="str">
         <v/>
       </c>
+      <c r="AN61" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -9370,6 +9553,9 @@
       <c r="AM62" t="str">
         <v/>
       </c>
+      <c r="AN62" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -9489,6 +9675,9 @@
       <c r="AM63" t="str">
         <v/>
       </c>
+      <c r="AN63" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -9608,6 +9797,9 @@
       <c r="AM64" t="str">
         <v/>
       </c>
+      <c r="AN64" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -9727,6 +9919,9 @@
       <c r="AM65" t="str">
         <v/>
       </c>
+      <c r="AN65" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -9846,6 +10041,9 @@
       <c r="AM66" t="str">
         <v/>
       </c>
+      <c r="AN66" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -9965,6 +10163,9 @@
       <c r="AM67" t="str">
         <v/>
       </c>
+      <c r="AN67" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -10084,6 +10285,9 @@
       <c r="AM68" t="str">
         <v/>
       </c>
+      <c r="AN68" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -10203,6 +10407,9 @@
       <c r="AM69" t="str">
         <v/>
       </c>
+      <c r="AN69" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -10322,6 +10529,9 @@
       <c r="AM70" t="str">
         <v/>
       </c>
+      <c r="AN70" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -10441,6 +10651,9 @@
       <c r="AM71" t="str">
         <v/>
       </c>
+      <c r="AN71" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -10560,6 +10773,9 @@
       <c r="AM72" t="str">
         <v/>
       </c>
+      <c r="AN72" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -10679,6 +10895,9 @@
       <c r="AM73" t="str">
         <v/>
       </c>
+      <c r="AN73" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -10798,6 +11017,9 @@
       <c r="AM74" t="str">
         <v/>
       </c>
+      <c r="AN74" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -10917,6 +11139,9 @@
       <c r="AM75" t="str">
         <v/>
       </c>
+      <c r="AN75" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -11036,6 +11261,9 @@
       <c r="AM76" t="str">
         <v/>
       </c>
+      <c r="AN76" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -11155,6 +11383,9 @@
       <c r="AM77" t="str">
         <v/>
       </c>
+      <c r="AN77" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -11274,6 +11505,9 @@
       <c r="AM78" t="str">
         <v/>
       </c>
+      <c r="AN78" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -11393,6 +11627,9 @@
       <c r="AM79" t="str">
         <v/>
       </c>
+      <c r="AN79" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -11512,6 +11749,9 @@
       <c r="AM80" t="str">
         <v/>
       </c>
+      <c r="AN80" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -11631,6 +11871,9 @@
       <c r="AM81" t="str">
         <v/>
       </c>
+      <c r="AN81" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -11750,6 +11993,9 @@
       <c r="AM82" t="str">
         <v/>
       </c>
+      <c r="AN82" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -11869,6 +12115,9 @@
       <c r="AM83" t="str">
         <v/>
       </c>
+      <c r="AN83" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -11988,6 +12237,9 @@
       <c r="AM84" t="str">
         <v/>
       </c>
+      <c r="AN84" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -12107,6 +12359,9 @@
       <c r="AM85" t="str">
         <v/>
       </c>
+      <c r="AN85" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -12226,6 +12481,9 @@
       <c r="AM86" t="str">
         <v/>
       </c>
+      <c r="AN86" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -12345,6 +12603,9 @@
       <c r="AM87" t="str">
         <v/>
       </c>
+      <c r="AN87" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -12464,6 +12725,9 @@
       <c r="AM88" t="str">
         <v/>
       </c>
+      <c r="AN88" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -12583,6 +12847,9 @@
       <c r="AM89" t="str">
         <v/>
       </c>
+      <c r="AN89" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -12702,6 +12969,9 @@
       <c r="AM90" t="str">
         <v/>
       </c>
+      <c r="AN90" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -12821,6 +13091,9 @@
       <c r="AM91" t="str">
         <v/>
       </c>
+      <c r="AN91" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -12940,6 +13213,9 @@
       <c r="AM92" t="str">
         <v/>
       </c>
+      <c r="AN92" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -13059,6 +13335,9 @@
       <c r="AM93" t="str">
         <v/>
       </c>
+      <c r="AN93" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -13178,6 +13457,9 @@
       <c r="AM94" t="str">
         <v/>
       </c>
+      <c r="AN94" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -13297,6 +13579,9 @@
       <c r="AM95" t="str">
         <v/>
       </c>
+      <c r="AN95" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -13416,6 +13701,9 @@
       <c r="AM96" t="str">
         <v/>
       </c>
+      <c r="AN96" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -13535,6 +13823,9 @@
       <c r="AM97" t="str">
         <v/>
       </c>
+      <c r="AN97" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -13654,6 +13945,9 @@
       <c r="AM98" t="str">
         <v/>
       </c>
+      <c r="AN98" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -13773,6 +14067,9 @@
       <c r="AM99" t="str">
         <v/>
       </c>
+      <c r="AN99" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -13892,6 +14189,9 @@
       <c r="AM100" t="str">
         <v/>
       </c>
+      <c r="AN100" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -14011,6 +14311,9 @@
       <c r="AM101" t="str">
         <v/>
       </c>
+      <c r="AN101" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -14130,6 +14433,9 @@
       <c r="AM102" t="str">
         <v/>
       </c>
+      <c r="AN102" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -14249,6 +14555,9 @@
       <c r="AM103" t="str">
         <v/>
       </c>
+      <c r="AN103" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -14368,6 +14677,9 @@
       <c r="AM104" t="str">
         <v/>
       </c>
+      <c r="AN104" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -14487,6 +14799,9 @@
       <c r="AM105" t="str">
         <v/>
       </c>
+      <c r="AN105" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -14606,6 +14921,9 @@
       <c r="AM106" t="str">
         <v/>
       </c>
+      <c r="AN106" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -14725,6 +15043,9 @@
       <c r="AM107" t="str">
         <v/>
       </c>
+      <c r="AN107" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -14844,6 +15165,9 @@
       <c r="AM108" t="str">
         <v/>
       </c>
+      <c r="AN108" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -14963,6 +15287,9 @@
       <c r="AM109" t="str">
         <v/>
       </c>
+      <c r="AN109" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -15082,6 +15409,9 @@
       <c r="AM110" t="str">
         <v/>
       </c>
+      <c r="AN110" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -15201,6 +15531,9 @@
       <c r="AM111" t="str">
         <v/>
       </c>
+      <c r="AN111" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -15320,6 +15653,9 @@
       <c r="AM112" t="str">
         <v/>
       </c>
+      <c r="AN112" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -15439,6 +15775,9 @@
       <c r="AM113" t="str">
         <v/>
       </c>
+      <c r="AN113" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -15558,6 +15897,9 @@
       <c r="AM114" t="str">
         <v/>
       </c>
+      <c r="AN114" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -15677,6 +16019,9 @@
       <c r="AM115" t="str">
         <v/>
       </c>
+      <c r="AN115" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -15796,6 +16141,9 @@
       <c r="AM116" t="str">
         <v/>
       </c>
+      <c r="AN116" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -15915,6 +16263,9 @@
       <c r="AM117" t="str">
         <v/>
       </c>
+      <c r="AN117" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -16034,6 +16385,9 @@
       <c r="AM118" t="str">
         <v/>
       </c>
+      <c r="AN118" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -16153,6 +16507,9 @@
       <c r="AM119" t="str">
         <v/>
       </c>
+      <c r="AN119" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -16272,6 +16629,9 @@
       <c r="AM120" t="str">
         <v/>
       </c>
+      <c r="AN120" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -16391,6 +16751,9 @@
       <c r="AM121" t="str">
         <v/>
       </c>
+      <c r="AN121" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -16510,6 +16873,9 @@
       <c r="AM122" t="str">
         <v/>
       </c>
+      <c r="AN122" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -16629,6 +16995,9 @@
       <c r="AM123" t="str">
         <v/>
       </c>
+      <c r="AN123" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -16748,6 +17117,9 @@
       <c r="AM124" t="str">
         <v/>
       </c>
+      <c r="AN124" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -16867,6 +17239,9 @@
       <c r="AM125" t="str">
         <v/>
       </c>
+      <c r="AN125" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -16986,6 +17361,9 @@
       <c r="AM126" t="str">
         <v/>
       </c>
+      <c r="AN126" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -17105,6 +17483,9 @@
       <c r="AM127" t="str">
         <v/>
       </c>
+      <c r="AN127" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -17224,6 +17605,9 @@
       <c r="AM128" t="str">
         <v/>
       </c>
+      <c r="AN128" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -17343,6 +17727,9 @@
       <c r="AM129" t="str">
         <v/>
       </c>
+      <c r="AN129" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -17462,6 +17849,9 @@
       <c r="AM130" t="str">
         <v/>
       </c>
+      <c r="AN130" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -17581,6 +17971,9 @@
       <c r="AM131" t="str">
         <v/>
       </c>
+      <c r="AN131" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -17700,6 +18093,9 @@
       <c r="AM132" t="str">
         <v/>
       </c>
+      <c r="AN132" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -17819,6 +18215,9 @@
       <c r="AM133" t="str">
         <v/>
       </c>
+      <c r="AN133" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -17938,6 +18337,9 @@
       <c r="AM134" t="str">
         <v/>
       </c>
+      <c r="AN134" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -18057,6 +18459,9 @@
       <c r="AM135" t="str">
         <v/>
       </c>
+      <c r="AN135" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -18176,6 +18581,9 @@
       <c r="AM136" t="str">
         <v/>
       </c>
+      <c r="AN136" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -18295,6 +18703,9 @@
       <c r="AM137" t="str">
         <v/>
       </c>
+      <c r="AN137" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -18414,6 +18825,9 @@
       <c r="AM138" t="str">
         <v/>
       </c>
+      <c r="AN138" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -18533,6 +18947,9 @@
       <c r="AM139" t="str">
         <v/>
       </c>
+      <c r="AN139" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -18652,6 +19069,9 @@
       <c r="AM140" t="str">
         <v/>
       </c>
+      <c r="AN140" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -18771,6 +19191,9 @@
       <c r="AM141" t="str">
         <v/>
       </c>
+      <c r="AN141" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -18890,10 +19313,13 @@
       <c r="AM142" t="str">
         <v/>
       </c>
+      <c r="AN142" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AM142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN142"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
@@ -473,7 +473,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I2" t="str">
-        <v>images/daiwa_reels/IM_Z_リミットブレイカー_TW_HD-C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM_Z_%E3%83%AA%E3%83%9F%E3%83%83%E3%83%88%E3%83%96%E3%83%AC%E3%82%A4%E3%82%AB%E3%83%BC_TW_HD-C_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -524,7 +524,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I3" t="str">
-        <v>images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -575,7 +575,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I4" t="str">
-        <v>images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -627,7 +627,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I5" t="str">
-        <v>images/daiwa_reels/スティーズ_リミテッド_CT_SV_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA_%E3%83%AA%E3%83%9F%E3%83%86%E3%83%83%E3%83%89_CT_SV_TW_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -678,7 +678,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I6" t="str">
-        <v>images/daiwa_reels/スティーズ_SV_ライト_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA_SV_%E3%83%A9%E3%82%A4%E3%83%88_TW_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -727,7 +727,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I7" t="str">
-        <v>images/daiwa_reels/スティーズ_SV_TW100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA_SV_TW100_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -829,7 +829,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I9" t="str">
-        <v>images/daiwa_reels/リョウガ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AA%E3%83%A7%E3%82%A6%E3%82%AC_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -931,7 +931,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I11" t="str">
-        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_tw_hd_22/__icsFiles/afieldfile/2022/04/08/main.jpg?rev=dd8848fe936e4b268b8bdb9e4b33a4df</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -983,7 +983,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I12" t="str">
-        <v>images/daiwa_reels/月下美人_BF_TW_PE_SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1085,7 +1085,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I14" t="str">
-        <v>images/daiwa_reels/シルバーウルフ_CT_SV_TW_PE_SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%A6%E3%83%AB%E3%83%95_CT_SV_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1238,7 +1238,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I17" t="str">
-        <v>images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1291,7 +1291,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I18" t="str">
-        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/salt_rl/silverwolf_sv_tw/__icsFiles/artimage/2022/04/01/c_041110017/main_tx_im01_1.jpg?rev=6d195f85744643bda6ef194759f4c436</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1340,7 +1340,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I19" t="str">
-        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/silvercreek_air_tw_sc/__icsFiles/artimage/2022/03/29/c_041101086/main_tx_im01_3.jpg?rev=d0db4f46700344e7893e0f732daf59a2</v>
+        <v/>
       </c>
       <c r="J19" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1443,7 +1443,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I21" t="str">
-        <v>images/daiwa_reels/アルファスBF_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A2%E3%83%AB%E3%83%95%E3%82%A1%E3%82%B9BF_TW_main.jpg</v>
       </c>
       <c r="J21" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1496,7 +1496,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I22" t="str">
-        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_sv_tw21/__icsFiles/artimage/2022/05/02/c_041101076/main_bg02_1.jpg?rev=eb0a7bf7b3584f528da16f4584f37003</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1547,7 +1547,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I23" t="str">
-        <v>images/daiwa_reels/ソルティスト_TW_PE_SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%B9%E3%83%88_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J23" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1699,7 +1699,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I26" t="str">
-        <v>images/daiwa_reels/タトゥーラ_BF_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_BF_TW_main.jpg</v>
       </c>
       <c r="J26" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1752,7 +1752,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I27" t="str">
-        <v>images/daiwa_reels/タトゥーラ_TW_200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_TW_200_main.jpg</v>
       </c>
       <c r="J27" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1806,7 +1806,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I28" t="str">
-        <v>images/daiwa_reels/タトゥーラ_SV_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_SV_TW_main.jpg</v>
       </c>
       <c r="J28" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1858,7 +1858,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I29" t="str">
-        <v>images/daiwa_reels/タトゥーラ_TW_100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_TW_100_main.jpg</v>
       </c>
       <c r="J29" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -1910,7 +1910,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I30" t="str">
-        <v>images/daiwa_reels/バス__X__100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%90%E3%82%B9__X__100_main.jpg</v>
       </c>
       <c r="J30" t="str">
         <v>2026-04-09T06:29:15.200Z</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_baitcasting_reel_import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24280" windowHeight="12940" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30240" windowHeight="14640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reel" sheetId="1" state="visible" r:id="rId1"/>
@@ -1078,6 +1078,10 @@
   </sheetPr>
   <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
+  <cols>
+    <col width="40.9285714285714" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1195,6 +1199,11 @@
           <t>SILVER WOLF CT SV TW PE SPECIAL</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>银狼</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>精细,海水</t>
@@ -1270,6 +1279,11 @@
           <t>TATULA BF TW</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>蜘蛛</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>2026</t>
@@ -1355,6 +1369,11 @@
           <t>月下美人 BF TW PE SP</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>月下美人</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>2026</t>
@@ -1440,6 +1459,11 @@
           <t>STEEZ SV LIGHT TW</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>精细,泛用,bass</t>
@@ -1515,6 +1539,11 @@
           <t>RYOGA</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>肉鸽</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>2026</t>
@@ -1595,6 +1624,11 @@
           <t>SALTIGA 10</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>赛尔迪迦</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1675,6 +1709,11 @@
           <t>SALTIGA 35</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>赛尔迪迦</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1755,6 +1794,11 @@
           <t>STEEZ LIMITED CT SV TW</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>精细,bass</t>
@@ -1830,6 +1874,11 @@
           <t>SALTIGA 300</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>赛尔迪迦</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1910,6 +1959,11 @@
           <t>TATULA SV TW 100</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>蜘蛛</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1995,6 +2049,11 @@
           <t>ALPHAS BF TW</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>阿尔法</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>2025</t>
@@ -2080,6 +2139,11 @@
           <t>STEEZ SV TW</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>2024</t>
@@ -2165,6 +2229,11 @@
           <t>TATULA TW 100</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>蜘蛛</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>2024</t>
@@ -2250,6 +2319,11 @@
           <t>SALTIGA 15</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>赛尔迪迦</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>2022</t>
@@ -2405,6 +2479,11 @@
           <t>STEEZ A II TW</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>2022</t>
@@ -2490,6 +2569,11 @@
           <t>ZILLION TW HD</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>子龙</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>2022</t>
@@ -2575,6 +2659,11 @@
           <t>SALTIGA IC</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>赛尔迪迦</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>2021</t>
@@ -2650,6 +2739,11 @@
           <t>ZILLION SV TW</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>子龙</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>2021</t>
@@ -2735,6 +2829,11 @@
           <t>ALPHAS SV TW</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>阿尔法</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>21/22 ALPHAS SV TW</t>
@@ -2815,6 +2914,11 @@
           <t>STEEZ LTD SV TW</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>2021</t>
@@ -2970,6 +3074,11 @@
           <t>TATULA TW 300/400</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>蜘蛛</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>强力,海水,bass</t>
@@ -3115,6 +3224,11 @@
           <t>STEEZ CT SV TW</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>精细,bass</t>
@@ -3190,6 +3304,11 @@
           <t>STEEZ AIR TW</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>史帝兹</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>2020</t>
@@ -3275,6 +3394,11 @@
           <t>MORETHAN PE TW</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>猫赞</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>远投,海水</t>
@@ -3510,6 +3634,11 @@
           <t>SALTIST TW PE SPECIAL</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>赛尔迪</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>2023</t>
@@ -3593,6 +3722,11 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>TATULA TW 200</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>蜘蛛</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -23578,7 +23712,7 @@
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / SV CONCEPT / MAGFORCE AIR / UTD / DRAG CLICK / G1 CT SV spool</t>
+          <t>TWS / UTD / ZERO ADJUSTER / ZERO SHAFT / Air Brake System / SV CONCEPT / CT CONCEPT / CT SV spool / G1 spool</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -23745,7 +23879,7 @@
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / SV CONCEPT / MAGFORCE AIR / UTD / DRAG CLICK / G1 CT SV spool</t>
+          <t>TWS / UTD / ZERO ADJUSTER / ZERO SHAFT / Air Brake System / SV CONCEPT / CT CONCEPT / CT SV spool / G1 spool</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -23912,7 +24046,7 @@
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / SV CONCEPT / MAGFORCE AIR / UTD / DRAG CLICK / G1 CT SV spool</t>
+          <t>TWS / UTD / ZERO ADJUSTER / ZERO SHAFT / Air Brake System / SV CONCEPT / CT CONCEPT / CT SV spool / G1 spool</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -24079,7 +24213,7 @@
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / SV CONCEPT / MAGFORCE AIR / UTD / DRAG CLICK / G1 CT SV spool</t>
+          <t>TWS / UTD / ZERO ADJUSTER / ZERO SHAFT / Air Brake System / SV CONCEPT / CT CONCEPT / CT SV spool / G1 spool</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -24246,7 +24380,7 @@
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / SV CONCEPT / MAGFORCE AIR / UTD / DRAG CLICK / G1 CT SV spool</t>
+          <t>TWS / UTD / ZERO ADJUSTER / ZERO SHAFT / Air Brake System / SV CONCEPT / CT CONCEPT / CT SV spool / G1 spool</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -24413,7 +24547,7 @@
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / SV CONCEPT / MAGFORCE AIR / UTD / DRAG CLICK / G1 CT SV spool</t>
+          <t>TWS / UTD / ZERO ADJUSTER / ZERO SHAFT / Air Brake System / SV CONCEPT / CT CONCEPT / CT SV spool / G1 spool</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -24580,7 +24714,7 @@
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / MAGFORCE AIR / AIR spool / UTD / G1 AIR spool</t>
+          <t>HYPERDRIVE DESIGN / HYPERDRIVE DIGIGEAR / HYPER DOUBLE SUPPORT / HYPER ARMED HOUSING / HYPER TOUGH CLUTCH / ZERO ADJUSTER / Air Brake System / SPEED SHAFT / TWS / UTD / AIR spool / G1 drive gear / Air Metal Housing</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -24747,7 +24881,7 @@
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / MAGFORCE AIR / AIR spool / UTD / G1 AIR spool</t>
+          <t>HYPERDRIVE DESIGN / HYPERDRIVE DIGIGEAR / HYPER DOUBLE SUPPORT / HYPER ARMED HOUSING / HYPER TOUGH CLUTCH / ZERO ADJUSTER / Air Brake System / SPEED SHAFT / TWS / UTD / AIR spool / G1 drive gear / Air Metal Housing</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
@@ -24914,7 +25048,7 @@
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / MAGFORCE AIR / AIR spool / UTD / G1 AIR spool</t>
+          <t>HYPERDRIVE DESIGN / HYPERDRIVE DIGIGEAR / HYPER DOUBLE SUPPORT / HYPER ARMED HOUSING / HYPER TOUGH CLUTCH / ZERO ADJUSTER / Air Brake System / SPEED SHAFT / TWS / UTD / AIR spool / G1 drive gear / Air Metal Housing</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -25081,7 +25215,7 @@
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>Air Metal / TWS / MAGFORCE AIR / AIR spool / UTD / G1 AIR spool</t>
+          <t>HYPERDRIVE DESIGN / HYPERDRIVE DIGIGEAR / HYPER DOUBLE SUPPORT / HYPER ARMED HOUSING / HYPER TOUGH CLUTCH / ZERO ADJUSTER / Air Brake System / SPEED SHAFT / TWS / UTD / AIR spool / G1 drive gear / Air Metal Housing</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
